--- a/data_processed/results_OLS_kg_CO2e_per_capitaincome.xlsx
+++ b/data_processed/results_OLS_kg_CO2e_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.5745" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.547" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4099.763401281622</v>
+        <v>4263.989737233854</v>
       </c>
       <c r="D2" t="n">
-        <v>7.101668913643054e-123</v>
+        <v>7.905561188203719e-117</v>
       </c>
     </row>
     <row r="3">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>279.4732159353587</v>
+        <v>282.069039286815</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.64933453866401</v>
+        <v>-581.9564986236326</v>
       </c>
       <c r="D4" t="n">
-        <v>0.195197249219619</v>
+        <v>7.230214819450457e-55</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>64.32719197891416</v>
+        <v>31.92756687095513</v>
       </c>
       <c r="D5" t="n">
-        <v>7.839750288049641e-29</v>
+        <v>2.677560963513571e-177</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-316.8962454799068</v>
+        <v>-251.8828937527473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.816564144512011e-226</v>
+        <v>3.595139940328596e-40</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0158274417725057</v>
+        <v>34.93378711029892</v>
       </c>
       <c r="D7" t="n">
-        <v>1.476652744388229e-14</v>
+        <v>1.668868450907553e-05</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.1034979945272919</v>
+        <v>-328.2518104993075</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001414449008667314</v>
+        <v>1.438875697815189e-189</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_train</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1062.083631349476</v>
+        <v>0.005486701690466</v>
       </c>
       <c r="D9" t="n">
-        <v>1.893651040360714e-207</v>
+        <v>0.02466910617382133</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.18930188915738</v>
+        <v>-0.03087544128997771</v>
       </c>
       <c r="D10" t="n">
-        <v>5.412024495034457e-141</v>
+        <v>0.4359608864711904</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +595,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>districtheating_pc</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>47.14312382525765</v>
+        <v>-813.0832340065729</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0002794076319305342</v>
+        <v>6.792731393415707e-06</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>heatpump_pc</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-532.4015964935396</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.01394291349655508</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>solarcapacity</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-505.5330978847329</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.134448619717157e-181</v>
       </c>
     </row>
   </sheetData>
